--- a/entertainment_forms/015_festival_headliner_poll--entertainment_forms.xlsx
+++ b/entertainment_forms/015_festival_headliner_poll--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'headliner_a'}</t>
+          <t>headliner_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Headliner A'}</t>
+          <t>Headliner A</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'headliner_b'}</t>
+          <t>headliner_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Headliner B'}</t>
+          <t>Headliner B</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'headliner_c'}</t>
+          <t>headliner_c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Headliner C'}</t>
+          <t>Headliner C</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
